--- a/public/templates/report-generator-template.xlsx
+++ b/public/templates/report-generator-template.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abyos\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abyos\Documents\GitHub\ReportGenrator\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{241B28CC-6B6E-4F50-ADF8-AA2AB74E77A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52EBDA03-84C1-41C2-8B77-DC0AD2B02F18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="4995" windowWidth="28800" windowHeight="15435" xr2:uid="{ECEE3F40-80EB-4313-9D59-FED83186C7B1}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="28800" windowHeight="15345" activeTab="1" xr2:uid="{ECEE3F40-80EB-4313-9D59-FED83186C7B1}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Unit Type 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Unit Type 2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="10">
   <si>
     <t>Unit ID</t>
   </si>
@@ -63,19 +64,10 @@
     <t>70B3D5A9F017C80F</t>
   </si>
   <si>
-    <t>70B3D5A9F013DE16</t>
-  </si>
-  <si>
     <t>70B3D5A9F0173333</t>
   </si>
   <si>
-    <t>70B3D5A9F013DE18</t>
-  </si>
-  <si>
     <t>Unit Type 1</t>
-  </si>
-  <si>
-    <t>Unit Type 2</t>
   </si>
 </sst>
 </file>
@@ -624,7 +616,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -721,7 +713,7 @@
     </row>
     <row r="6" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4">
         <v>915.2</v>
@@ -757,195 +749,149 @@
       </c>
       <c r="E8" s="6"/>
     </row>
-    <row r="10" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-    </row>
-    <row r="11" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>4</v>
-      </c>
+    <row r="10" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+    </row>
+    <row r="11" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
     </row>
     <row r="12" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="4">
-        <v>915.2</v>
-      </c>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4">
-        <f>F12+$L$3</f>
-        <v>19.296999999999997</v>
-      </c>
-      <c r="E12" s="4"/>
-      <c r="F12" s="3">
-        <v>-16.68</v>
-      </c>
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
     </row>
     <row r="13" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="5">
-        <v>922.2</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5">
-        <f>F13+$L$4</f>
-        <v>19.333999999999996</v>
-      </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="3">
-        <v>-16.600000000000001</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="6">
-        <v>927.8</v>
-      </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6">
-        <f>F14+$L$5</f>
-        <v>19.124000000000002</v>
-      </c>
-      <c r="E14" s="6"/>
-      <c r="F14" s="3">
-        <v>-16.68</v>
-      </c>
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+    </row>
+    <row r="14" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
     </row>
     <row r="15" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="4">
-        <v>915.2</v>
-      </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4">
-        <f>F15+$L$3</f>
-        <v>19.296999999999997</v>
-      </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="3">
-        <v>-16.68</v>
-      </c>
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
     </row>
     <row r="16" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="5">
-        <v>922.2</v>
-      </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5">
-        <f>F16+$L$4</f>
-        <v>19.333999999999996</v>
-      </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="3">
-        <v>-16.600000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="14"/>
-      <c r="B17" s="6">
-        <v>927.8</v>
-      </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6">
-        <f>F17+$L$5</f>
-        <v>19.124000000000002</v>
-      </c>
-      <c r="E17" s="6"/>
-      <c r="F17" s="3">
-        <v>-16.68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" s="4">
-        <v>915.2</v>
-      </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4">
-        <f>F18+$L$3</f>
-        <v>19.296999999999997</v>
-      </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="3">
-        <v>-16.68</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="5">
-        <v>922.2</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5">
-        <f>F19+$L$4</f>
-        <v>19.333999999999996</v>
-      </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="3">
-        <v>-16.600000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14"/>
-      <c r="B20" s="6">
-        <v>927.8</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="6">
-        <f>F20+$L$5</f>
-        <v>19.124000000000002</v>
-      </c>
-      <c r="E20" s="6"/>
-      <c r="F20" s="3">
-        <v>-16.68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+    </row>
+    <row r="17" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+    </row>
+    <row r="18" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+    </row>
+    <row r="19" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+    </row>
+    <row r="20" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+    </row>
+    <row r="21" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
     </row>
-    <row r="22" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
     </row>
-    <row r="23" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
     </row>
-    <row r="24" spans="1:6" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24"/>
@@ -953,12 +899,323 @@
       <c r="E24"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A15:A17"/>
+  <mergeCells count="2">
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A12:A14"/>
-    <mergeCell ref="A18:A20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E613579E-5504-4097-BD46-BA94FFF208D3}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="36.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.125" style="3"/>
+    <col min="7" max="10" width="9.125" style="2"/>
+    <col min="11" max="11" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="2" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4">
+        <v>915.2</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4">
+        <f>F3+$L$3</f>
+        <v>18.416999999999998</v>
+      </c>
+      <c r="E3" s="4"/>
+      <c r="F3" s="3">
+        <v>-17.559999999999999</v>
+      </c>
+      <c r="K3" s="2">
+        <v>915.2</v>
+      </c>
+      <c r="L3" s="2">
+        <v>35.976999999999997</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="5">
+        <v>922.2</v>
+      </c>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5">
+        <f>F4+$L$4</f>
+        <v>17.553999999999998</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="3">
+        <v>-18.38</v>
+      </c>
+      <c r="K4" s="2">
+        <v>922.2</v>
+      </c>
+      <c r="L4" s="2">
+        <v>35.933999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="14"/>
+      <c r="B5" s="6">
+        <v>927.8</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6">
+        <f>F5+$L$5</f>
+        <v>16.714000000000002</v>
+      </c>
+      <c r="E5" s="6"/>
+      <c r="F5" s="3">
+        <v>-19.09</v>
+      </c>
+      <c r="K5" s="2">
+        <v>927.8</v>
+      </c>
+      <c r="L5" s="2">
+        <v>35.804000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4">
+        <v>915.2</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4">
+        <f>F6+$L$3</f>
+        <v>35.976999999999997</v>
+      </c>
+      <c r="E6" s="4"/>
+    </row>
+    <row r="7" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="13"/>
+      <c r="B7" s="5">
+        <v>922.2</v>
+      </c>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5">
+        <f>F7+$L$4</f>
+        <v>35.933999999999997</v>
+      </c>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" ht="36.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
+      <c r="B8" s="6">
+        <v>927.8</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6">
+        <f>F8+$L$5</f>
+        <v>35.804000000000002</v>
+      </c>
+      <c r="E8" s="6"/>
+    </row>
+    <row r="10" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10"/>
+      <c r="B10"/>
+      <c r="C10"/>
+      <c r="D10"/>
+      <c r="E10"/>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10"/>
+    </row>
+    <row r="11" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11"/>
+      <c r="B11"/>
+      <c r="C11"/>
+      <c r="D11"/>
+      <c r="E11"/>
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="I11"/>
+    </row>
+    <row r="12" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12"/>
+      <c r="B12"/>
+      <c r="C12"/>
+      <c r="D12"/>
+      <c r="E12"/>
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="I12"/>
+    </row>
+    <row r="13" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13"/>
+      <c r="B13"/>
+      <c r="C13"/>
+      <c r="D13"/>
+      <c r="E13"/>
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="I13"/>
+    </row>
+    <row r="14" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14"/>
+      <c r="B14"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+    </row>
+    <row r="15" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15"/>
+      <c r="B15"/>
+      <c r="C15"/>
+      <c r="D15"/>
+      <c r="E15"/>
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+    </row>
+    <row r="16" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16"/>
+      <c r="B16"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="E16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16"/>
+    </row>
+    <row r="17" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17"/>
+      <c r="B17"/>
+      <c r="C17"/>
+      <c r="D17"/>
+      <c r="E17"/>
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+    </row>
+    <row r="18" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18"/>
+      <c r="B18"/>
+      <c r="C18"/>
+      <c r="D18"/>
+      <c r="E18"/>
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="I18"/>
+    </row>
+    <row r="19" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19"/>
+      <c r="B19"/>
+      <c r="C19"/>
+      <c r="D19"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="I19"/>
+    </row>
+    <row r="20" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20"/>
+      <c r="B20"/>
+      <c r="C20"/>
+      <c r="D20"/>
+      <c r="E20"/>
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="I20"/>
+    </row>
+    <row r="21" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="I21"/>
+    </row>
+    <row r="22" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+    </row>
+    <row r="23" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23"/>
+      <c r="D23"/>
+      <c r="E23"/>
+    </row>
+    <row r="24" spans="1:9" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -973,6 +1230,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100724179348409134E8DF599AA05313BB4" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="af30210fd63a6d369de7fc440d9198f2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="7aa56756-527e-4eff-9208-0b4e58a0c97f" xmlns:ns4="d3816fb4-04a0-49c6-a585-a8ea72fd59a3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2581bf2d024aad4fc3fd29ce78935bb0" ns3:_="" ns4:_="">
     <xsd:import namespace="7aa56756-527e-4eff-9208-0b4e58a0c97f"/>
@@ -1211,15 +1477,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D57F0157-5ABB-467B-BB05-7F492F5F6EF0}">
   <ds:schemaRefs>
@@ -1231,6 +1488,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D529D985-65F1-4189-89DC-0CE527EC86E5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DB5256BE-71E9-41A2-9214-29B47C378161}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1247,12 +1512,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D529D985-65F1-4189-89DC-0CE527EC86E5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>